--- a/outputs/fifa_team_statistics/excel_por_categoria/Distribution.xlsx
+++ b/outputs/fifa_team_statistics/excel_por_categoria/Distribution.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Datos limpios" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Resumen numerico" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos limpios" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen numerico" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -627,32 +627,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F5" t="n">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G5" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H5" t="n">
-        <v>2285</v>
+        <v>2338</v>
       </c>
       <c r="I5" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J5" t="n">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="K5" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -666,32 +666,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="E6" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F6" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G6" t="n">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="H6" t="n">
-        <v>2219</v>
+        <v>2285</v>
       </c>
       <c r="I6" t="n">
         <v>90</v>
       </c>
       <c r="J6" t="n">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="K6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="E7" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F7" t="n">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="G7" t="n">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="H7" t="n">
-        <v>2191</v>
+        <v>2248</v>
       </c>
       <c r="I7" t="n">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="J7" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="K7" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -744,32 +744,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>England</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="E8" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="F8" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="G8" t="n">
-        <v>57</v>
+        <v>118</v>
       </c>
       <c r="H8" t="n">
-        <v>2070</v>
+        <v>2219</v>
       </c>
       <c r="I8" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="J8" t="n">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="K8" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -783,32 +783,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E9" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F9" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="G9" t="n">
         <v>78</v>
       </c>
       <c r="H9" t="n">
-        <v>2039</v>
+        <v>2191</v>
       </c>
       <c r="I9" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J9" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K9" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -822,32 +822,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="G10" t="n">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="H10" t="n">
-        <v>1985</v>
+        <v>2070</v>
       </c>
       <c r="I10" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="J10" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K10" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E11" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F11" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G11" t="n">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="H11" t="n">
-        <v>1970</v>
+        <v>2053</v>
       </c>
       <c r="I11" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J11" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="K11" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -900,32 +900,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="E12" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G12" t="n">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="H12" t="n">
-        <v>1966</v>
+        <v>2039</v>
       </c>
       <c r="I12" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="J12" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="K12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -939,32 +939,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="E13" t="n">
         <v>25</v>
       </c>
       <c r="F13" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="G13" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H13" t="n">
-        <v>1899</v>
+        <v>1985</v>
       </c>
       <c r="I13" t="n">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="J13" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -978,32 +978,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="E14" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F14" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="G14" t="n">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="H14" t="n">
-        <v>1855</v>
+        <v>1970</v>
       </c>
       <c r="I14" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="J14" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K14" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Korea Republic</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="E15" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F15" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="G15" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="H15" t="n">
-        <v>1853</v>
+        <v>1966</v>
       </c>
       <c r="I15" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J15" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K15" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E16" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="F16" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="G16" t="n">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="H16" t="n">
-        <v>1849</v>
+        <v>1899</v>
       </c>
       <c r="I16" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="J16" t="n">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="K16" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
@@ -1095,32 +1095,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Türkiye</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="E17" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F17" t="n">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="G17" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="H17" t="n">
-        <v>1844</v>
+        <v>1855</v>
       </c>
       <c r="I17" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J17" t="n">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="K17" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Korea Republic</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E18" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F18" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="G18" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H18" t="n">
-        <v>1733</v>
+        <v>1853</v>
       </c>
       <c r="I18" t="n">
+        <v>89</v>
+      </c>
+      <c r="J18" t="n">
         <v>86</v>
       </c>
-      <c r="J18" t="n">
-        <v>67</v>
-      </c>
       <c r="K18" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>131</v>
+        <v>52</v>
       </c>
       <c r="E19" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F19" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="G19" t="n">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="H19" t="n">
-        <v>1730</v>
+        <v>1849</v>
       </c>
       <c r="I19" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J19" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="K19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="E20" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F20" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="G20" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H20" t="n">
-        <v>1690</v>
+        <v>1844</v>
       </c>
       <c r="I20" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J20" t="n">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="K20" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E21" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F21" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G21" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H21" t="n">
-        <v>1663</v>
+        <v>1733</v>
       </c>
       <c r="I21" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J21" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="K21" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -1290,32 +1290,32 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="E22" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F22" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G22" t="n">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="H22" t="n">
-        <v>1643</v>
+        <v>1730</v>
       </c>
       <c r="I22" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="J22" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="K22" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E23" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F23" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G23" t="n">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="H23" t="n">
-        <v>1629</v>
+        <v>1690</v>
       </c>
       <c r="I23" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J23" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K23" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
@@ -1368,32 +1368,32 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E24" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="F24" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="G24" t="n">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="H24" t="n">
-        <v>1628</v>
+        <v>1663</v>
       </c>
       <c r="I24" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J24" t="n">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K24" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="E25" t="n">
         <v>29</v>
       </c>
       <c r="F25" t="n">
+        <v>45</v>
+      </c>
+      <c r="G25" t="n">
         <v>58</v>
       </c>
-      <c r="G25" t="n">
-        <v>69</v>
-      </c>
       <c r="H25" t="n">
-        <v>1610</v>
+        <v>1629</v>
       </c>
       <c r="I25" t="n">
         <v>88</v>
       </c>
       <c r="J25" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="K25" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F26" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G26" t="n">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="H26" t="n">
-        <v>1569</v>
+        <v>1618</v>
       </c>
       <c r="I26" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J26" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="K26" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
@@ -1485,32 +1485,32 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="E27" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F27" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G27" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H27" t="n">
-        <v>1543</v>
+        <v>1569</v>
       </c>
       <c r="I27" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J27" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K27" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
@@ -1524,32 +1524,32 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E28" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F28" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G28" t="n">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="H28" t="n">
-        <v>1515</v>
+        <v>1543</v>
       </c>
       <c r="I28" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J28" t="n">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="K28" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
@@ -1563,32 +1563,32 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Congo DR</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="E29" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F29" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="G29" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="H29" t="n">
-        <v>1470</v>
+        <v>1515</v>
       </c>
       <c r="I29" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="J29" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
@@ -1602,32 +1602,32 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Congo DR</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="E30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F30" t="n">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="G30" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="H30" t="n">
-        <v>1467</v>
+        <v>1470</v>
       </c>
       <c r="I30" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="J30" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="K30" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31">
@@ -1641,32 +1641,32 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="E31" t="n">
         <v>21</v>
       </c>
       <c r="F31" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G31" t="n">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="H31" t="n">
-        <v>1445</v>
+        <v>1467</v>
       </c>
       <c r="I31" t="n">
         <v>87</v>
       </c>
       <c r="J31" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="K31" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -1680,32 +1680,32 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="E32" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F32" t="n">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="G32" t="n">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="H32" t="n">
-        <v>1377</v>
+        <v>1445</v>
       </c>
       <c r="I32" t="n">
         <v>87</v>
       </c>
       <c r="J32" t="n">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="K32" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
@@ -1719,32 +1719,32 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="E33" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F33" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="G33" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="H33" t="n">
-        <v>1335</v>
+        <v>1377</v>
       </c>
       <c r="I33" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="J33" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K33" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34">
@@ -1758,32 +1758,32 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="E34" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F34" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="G34" t="n">
         <v>54</v>
       </c>
       <c r="H34" t="n">
-        <v>1259</v>
+        <v>1335</v>
       </c>
       <c r="I34" t="n">
         <v>83</v>
       </c>
       <c r="J34" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K34" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35">
@@ -1797,32 +1797,32 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="E35" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F35" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G35" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H35" t="n">
-        <v>1175</v>
+        <v>1259</v>
       </c>
       <c r="I35" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J35" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K35" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36">
@@ -1836,32 +1836,32 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="E36" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F36" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G36" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H36" t="n">
-        <v>1169</v>
+        <v>1175</v>
       </c>
       <c r="I36" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="J36" t="n">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="K36" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37">
@@ -1875,32 +1875,32 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E37" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F37" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G37" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="H37" t="n">
-        <v>1159</v>
+        <v>1169</v>
       </c>
       <c r="I37" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="J37" t="n">
         <v>80</v>
       </c>
       <c r="K37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38">
@@ -2392,7 +2392,7 @@
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -2479,10 +2479,10 @@
         <v>48</v>
       </c>
       <c r="C3" t="n">
-        <v>56.20833333333334</v>
+        <v>57.97916666666666</v>
       </c>
       <c r="D3" t="n">
-        <v>24.82359750132525</v>
+        <v>26.09433751515087</v>
       </c>
       <c r="E3" t="n">
         <v>21</v>
@@ -2491,10 +2491,10 @@
         <v>36.75</v>
       </c>
       <c r="G3" t="n">
-        <v>52.5</v>
+        <v>53</v>
       </c>
       <c r="H3" t="n">
-        <v>67.75</v>
+        <v>77</v>
       </c>
       <c r="I3" t="n">
         <v>131</v>
@@ -2510,10 +2510,10 @@
         <v>48</v>
       </c>
       <c r="C4" t="n">
-        <v>24.66666666666667</v>
+        <v>24.5625</v>
       </c>
       <c r="D4" t="n">
-        <v>5.551819074453075</v>
+        <v>5.565494950366337</v>
       </c>
       <c r="E4" t="n">
         <v>14</v>
@@ -2525,7 +2525,7 @@
         <v>24.5</v>
       </c>
       <c r="H4" t="n">
-        <v>28.25</v>
+        <v>28</v>
       </c>
       <c r="I4" t="n">
         <v>37</v>
@@ -2541,10 +2541,10 @@
         <v>48</v>
       </c>
       <c r="C5" t="n">
-        <v>48.6875</v>
+        <v>48.60416666666666</v>
       </c>
       <c r="D5" t="n">
-        <v>11.62564342762941</v>
+        <v>11.47937944674143</v>
       </c>
       <c r="E5" t="n">
         <v>22</v>
@@ -2556,7 +2556,7 @@
         <v>49.5</v>
       </c>
       <c r="H5" t="n">
-        <v>57.25</v>
+        <v>57</v>
       </c>
       <c r="I5" t="n">
         <v>72</v>
@@ -2572,25 +2572,25 @@
         <v>48</v>
       </c>
       <c r="C6" t="n">
-        <v>65.64583333333333</v>
+        <v>67.52083333333333</v>
       </c>
       <c r="D6" t="n">
-        <v>17.92595833615329</v>
+        <v>20.05417087549485</v>
       </c>
       <c r="E6" t="n">
         <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>50.75</v>
+        <v>51.75</v>
       </c>
       <c r="G6" t="n">
-        <v>67</v>
+        <v>67.5</v>
       </c>
       <c r="H6" t="n">
-        <v>76.5</v>
+        <v>78.25</v>
       </c>
       <c r="I6" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7">
@@ -2603,22 +2603,22 @@
         <v>48</v>
       </c>
       <c r="C7" t="n">
-        <v>1583.729166666667</v>
+        <v>1629.916666666667</v>
       </c>
       <c r="D7" t="n">
-        <v>463.366531063616</v>
+        <v>484.5246775145384</v>
       </c>
       <c r="E7" t="n">
         <v>912</v>
       </c>
       <c r="F7" t="n">
-        <v>1151.5</v>
+        <v>1159</v>
       </c>
       <c r="G7" t="n">
-        <v>1589.5</v>
+        <v>1623.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1866</v>
+        <v>1973.75</v>
       </c>
       <c r="I7" t="n">
         <v>2721</v>
@@ -2634,10 +2634,10 @@
         <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>84.85416666666667</v>
+        <v>84.83333333333333</v>
       </c>
       <c r="D8" t="n">
-        <v>4.726519043598951</v>
+        <v>4.719057484932694</v>
       </c>
       <c r="E8" t="n">
         <v>72</v>
@@ -2665,10 +2665,10 @@
         <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>82.20833333333333</v>
+        <v>81.91666666666667</v>
       </c>
       <c r="D9" t="n">
-        <v>10.51029552661283</v>
+        <v>10.4511698079502</v>
       </c>
       <c r="E9" t="n">
         <v>56</v>
@@ -2680,7 +2680,7 @@
         <v>81</v>
       </c>
       <c r="H9" t="n">
-        <v>91</v>
+        <v>90.25</v>
       </c>
       <c r="I9" t="n">
         <v>100</v>
@@ -2696,10 +2696,10 @@
         <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>16.8125</v>
+        <v>17.35416666666667</v>
       </c>
       <c r="D10" t="n">
-        <v>5.836992266861783</v>
+        <v>6.054678456010175</v>
       </c>
       <c r="E10" t="n">
         <v>5</v>
@@ -2708,7 +2708,7 @@
         <v>13</v>
       </c>
       <c r="G10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="H10" t="n">
         <v>21</v>

--- a/outputs/fifa_team_statistics/excel_por_categoria/Distribution.xlsx
+++ b/outputs/fifa_team_statistics/excel_por_categoria/Distribution.xlsx
@@ -426,74 +426,62 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="26" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Rank</t>
+          <t>Crosses</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Team</t>
+          <t>Crossing Accuracy (%)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Crosses</t>
+          <t>Defensive Linebreaks Acc (%)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Crossing Accuracy (%)</t>
+          <t>Defensive Linebreaks Attempted</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Defensive Linebreaks Acc (%)</t>
+          <t>Passes</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Defensive Linebreaks Attempted</t>
+          <t>Passing Accuracy (%)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Passes</t>
+          <t>Switches of Play Acc (%)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Passing Accuracy (%)</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Switches of Play Acc (%)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Switches of Play Attempted</t>
         </is>
@@ -502,1873 +490,1489 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
+        <v>32</v>
+      </c>
+      <c r="C2" t="n">
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="E2" t="n">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="F2" t="n">
-        <v>56</v>
+        <v>2070</v>
       </c>
       <c r="G2" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H2" t="n">
-        <v>2721</v>
+        <v>95</v>
       </c>
       <c r="I2" t="n">
-        <v>90</v>
-      </c>
-      <c r="J2" t="n">
-        <v>71</v>
-      </c>
-      <c r="K2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Morocco</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="C3" t="n">
+        <v>33</v>
       </c>
       <c r="D3" t="n">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="E3" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="F3" t="n">
-        <v>53</v>
+        <v>1966</v>
       </c>
       <c r="G3" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H3" t="n">
-        <v>2627</v>
+        <v>85</v>
       </c>
       <c r="I3" t="n">
-        <v>89</v>
-      </c>
-      <c r="J3" t="n">
-        <v>81</v>
-      </c>
-      <c r="K3" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
+        <v>47</v>
+      </c>
+      <c r="C4" t="n">
+        <v>28</v>
       </c>
       <c r="D4" t="n">
-        <v>73</v>
+        <v>50</v>
       </c>
       <c r="E4" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="F4" t="n">
-        <v>57</v>
+        <v>1127</v>
       </c>
       <c r="G4" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H4" t="n">
-        <v>2395</v>
+        <v>56</v>
       </c>
       <c r="I4" t="n">
-        <v>90</v>
-      </c>
-      <c r="J4" t="n">
-        <v>94</v>
-      </c>
-      <c r="K4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Belgium</t>
-        </is>
+        <v>48</v>
+      </c>
+      <c r="C5" t="n">
+        <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="E5" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="F5" t="n">
-        <v>56</v>
+        <v>1467</v>
       </c>
       <c r="G5" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="H5" t="n">
-        <v>2338</v>
+        <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>88</v>
-      </c>
-      <c r="J5" t="n">
-        <v>75</v>
-      </c>
-      <c r="K5" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
+        <v>102</v>
+      </c>
+      <c r="C6" t="n">
+        <v>27</v>
       </c>
       <c r="D6" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E6" t="n">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="F6" t="n">
-        <v>68</v>
+        <v>2338</v>
       </c>
       <c r="G6" t="n">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="H6" t="n">
-        <v>2285</v>
+        <v>75</v>
       </c>
       <c r="I6" t="n">
-        <v>90</v>
-      </c>
-      <c r="J6" t="n">
-        <v>96</v>
-      </c>
-      <c r="K6" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Senegal</t>
-        </is>
+        <v>59</v>
+      </c>
+      <c r="C7" t="n">
+        <v>17</v>
       </c>
       <c r="D7" t="n">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="E7" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="F7" t="n">
-        <v>57</v>
+        <v>1618</v>
       </c>
       <c r="G7" t="n">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="H7" t="n">
-        <v>2248</v>
+        <v>76</v>
       </c>
       <c r="I7" t="n">
-        <v>88</v>
-      </c>
-      <c r="J7" t="n">
-        <v>90</v>
-      </c>
-      <c r="K7" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>England</t>
-        </is>
+        <v>73</v>
+      </c>
+      <c r="C8" t="n">
+        <v>29</v>
       </c>
       <c r="D8" t="n">
-        <v>118</v>
+        <v>57</v>
       </c>
       <c r="E8" t="n">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="F8" t="n">
-        <v>69</v>
+        <v>2395</v>
       </c>
       <c r="G8" t="n">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="H8" t="n">
-        <v>2219</v>
+        <v>94</v>
       </c>
       <c r="I8" t="n">
-        <v>90</v>
-      </c>
-      <c r="J8" t="n">
-        <v>73</v>
-      </c>
-      <c r="K8" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
+        <v>32</v>
+      </c>
+      <c r="C9" t="n">
+        <v>28</v>
       </c>
       <c r="D9" t="n">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="E9" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="F9" t="n">
-        <v>72</v>
+        <v>1064</v>
       </c>
       <c r="G9" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H9" t="n">
-        <v>2191</v>
+        <v>65</v>
       </c>
       <c r="I9" t="n">
-        <v>92</v>
-      </c>
-      <c r="J9" t="n">
-        <v>95</v>
-      </c>
-      <c r="K9" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Algeria</t>
-        </is>
+        <v>131</v>
+      </c>
+      <c r="C10" t="n">
+        <v>25</v>
       </c>
       <c r="D10" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="E10" t="n">
+        <v>94</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1730</v>
+      </c>
+      <c r="G10" t="n">
+        <v>83</v>
+      </c>
+      <c r="H10" t="n">
+        <v>81</v>
+      </c>
+      <c r="I10" t="n">
         <v>16</v>
-      </c>
-      <c r="F10" t="n">
-        <v>58</v>
-      </c>
-      <c r="G10" t="n">
-        <v>57</v>
-      </c>
-      <c r="H10" t="n">
-        <v>2070</v>
-      </c>
-      <c r="I10" t="n">
-        <v>91</v>
-      </c>
-      <c r="J10" t="n">
-        <v>95</v>
-      </c>
-      <c r="K10" t="n">
-        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
+        <v>48</v>
+      </c>
+      <c r="C11" t="n">
+        <v>29</v>
       </c>
       <c r="D11" t="n">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="E11" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>59</v>
+        <v>1629</v>
       </c>
       <c r="G11" t="n">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="H11" t="n">
-        <v>2053</v>
+        <v>91</v>
       </c>
       <c r="I11" t="n">
-        <v>86</v>
-      </c>
-      <c r="J11" t="n">
-        <v>81</v>
-      </c>
-      <c r="K11" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Congo DR</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
+        <v>64</v>
+      </c>
+      <c r="C12" t="n">
+        <v>22</v>
       </c>
       <c r="D12" t="n">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="E12" t="n">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="F12" t="n">
-        <v>60</v>
+        <v>1470</v>
       </c>
       <c r="G12" t="n">
+        <v>81</v>
+      </c>
+      <c r="H12" t="n">
         <v>78</v>
       </c>
-      <c r="H12" t="n">
-        <v>2039</v>
-      </c>
       <c r="I12" t="n">
-        <v>88</v>
-      </c>
-      <c r="J12" t="n">
-        <v>82</v>
-      </c>
-      <c r="K12" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ecuador</t>
-        </is>
+        <v>45</v>
+      </c>
+      <c r="C13" t="n">
+        <v>18</v>
       </c>
       <c r="D13" t="n">
+        <v>52</v>
+      </c>
+      <c r="E13" t="n">
+        <v>61</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1515</v>
+      </c>
+      <c r="G13" t="n">
         <v>88</v>
       </c>
-      <c r="E13" t="n">
-        <v>25</v>
-      </c>
-      <c r="F13" t="n">
-        <v>44</v>
-      </c>
-      <c r="G13" t="n">
-        <v>93</v>
-      </c>
       <c r="H13" t="n">
-        <v>1985</v>
+        <v>76</v>
       </c>
       <c r="I13" t="n">
-        <v>86</v>
-      </c>
-      <c r="J13" t="n">
-        <v>90</v>
-      </c>
-      <c r="K13" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Côte d'Ivoire</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="C14" t="n">
+        <v>29</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="E14" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F14" t="n">
-        <v>53</v>
+        <v>968</v>
       </c>
       <c r="G14" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H14" t="n">
-        <v>1970</v>
+        <v>100</v>
       </c>
       <c r="I14" t="n">
-        <v>88</v>
-      </c>
-      <c r="J14" t="n">
-        <v>92</v>
-      </c>
-      <c r="K14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
+        <v>50</v>
+      </c>
+      <c r="C15" t="n">
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="E15" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="F15" t="n">
-        <v>54</v>
+        <v>1102</v>
       </c>
       <c r="G15" t="n">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="H15" t="n">
-        <v>1966</v>
+        <v>75</v>
       </c>
       <c r="I15" t="n">
-        <v>91</v>
-      </c>
-      <c r="J15" t="n">
-        <v>85</v>
-      </c>
-      <c r="K15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Côte d'Ivoire</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
+        <v>78</v>
+      </c>
+      <c r="C16" t="n">
+        <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E16" t="n">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="F16" t="n">
-        <v>60</v>
+        <v>1970</v>
       </c>
       <c r="G16" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="H16" t="n">
-        <v>1899</v>
+        <v>92</v>
       </c>
       <c r="I16" t="n">
-        <v>92</v>
-      </c>
-      <c r="J16" t="n">
-        <v>84</v>
-      </c>
-      <c r="K16" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>South Africa</t>
-        </is>
+        <v>88</v>
+      </c>
+      <c r="C17" t="n">
+        <v>25</v>
       </c>
       <c r="D17" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E17" t="n">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="F17" t="n">
-        <v>41</v>
+        <v>1985</v>
       </c>
       <c r="G17" t="n">
-        <v>63</v>
+        <v>86</v>
       </c>
       <c r="H17" t="n">
-        <v>1855</v>
+        <v>90</v>
       </c>
       <c r="I17" t="n">
-        <v>85</v>
-      </c>
-      <c r="J17" t="n">
-        <v>85</v>
-      </c>
-      <c r="K17" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Korea Republic</t>
-        </is>
+        <v>53</v>
+      </c>
+      <c r="C18" t="n">
+        <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="E18" t="n">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="F18" t="n">
-        <v>60</v>
+        <v>1543</v>
       </c>
       <c r="G18" t="n">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="H18" t="n">
-        <v>1853</v>
+        <v>96</v>
       </c>
       <c r="I18" t="n">
-        <v>89</v>
-      </c>
-      <c r="J18" t="n">
-        <v>86</v>
-      </c>
-      <c r="K18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>England</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
+        <v>118</v>
+      </c>
+      <c r="C19" t="n">
+        <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="E19" t="n">
-        <v>37</v>
+        <v>118</v>
       </c>
       <c r="F19" t="n">
-        <v>43</v>
+        <v>2219</v>
       </c>
       <c r="G19" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="H19" t="n">
-        <v>1849</v>
+        <v>73</v>
       </c>
       <c r="I19" t="n">
-        <v>86</v>
-      </c>
-      <c r="J19" t="n">
-        <v>71</v>
-      </c>
-      <c r="K19" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Türkiye</t>
-        </is>
+        <v>66</v>
+      </c>
+      <c r="C20" t="n">
+        <v>17</v>
       </c>
       <c r="D20" t="n">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="E20" t="n">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="F20" t="n">
-        <v>60</v>
+        <v>2285</v>
       </c>
       <c r="G20" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="H20" t="n">
-        <v>1844</v>
+        <v>96</v>
       </c>
       <c r="I20" t="n">
-        <v>87</v>
-      </c>
-      <c r="J20" t="n">
-        <v>73</v>
-      </c>
-      <c r="K20" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
+        <v>108</v>
+      </c>
+      <c r="C21" t="n">
+        <v>22</v>
       </c>
       <c r="D21" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="E21" t="n">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="F21" t="n">
-        <v>47</v>
+        <v>2721</v>
       </c>
       <c r="G21" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="H21" t="n">
-        <v>1733</v>
+        <v>71</v>
       </c>
       <c r="I21" t="n">
-        <v>86</v>
-      </c>
-      <c r="J21" t="n">
-        <v>67</v>
-      </c>
-      <c r="K21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
+        <v>33</v>
+      </c>
+      <c r="C22" t="n">
+        <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>131</v>
+        <v>51</v>
       </c>
       <c r="E22" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="F22" t="n">
-        <v>56</v>
+        <v>1007</v>
       </c>
       <c r="G22" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="H22" t="n">
-        <v>1730</v>
+        <v>88</v>
       </c>
       <c r="I22" t="n">
-        <v>83</v>
-      </c>
-      <c r="J22" t="n">
-        <v>81</v>
-      </c>
-      <c r="K22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
+        <v>42</v>
+      </c>
+      <c r="C23" t="n">
+        <v>24</v>
       </c>
       <c r="D23" t="n">
+        <v>40</v>
+      </c>
+      <c r="E23" t="n">
         <v>42</v>
       </c>
-      <c r="E23" t="n">
-        <v>31</v>
-      </c>
       <c r="F23" t="n">
-        <v>41</v>
+        <v>1098</v>
       </c>
       <c r="G23" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="H23" t="n">
-        <v>1690</v>
+        <v>100</v>
       </c>
       <c r="I23" t="n">
-        <v>86</v>
-      </c>
-      <c r="J23" t="n">
-        <v>82</v>
-      </c>
-      <c r="K23" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>IR Iran</t>
         </is>
       </c>
       <c r="B24" t="n">
+        <v>40</v>
+      </c>
+      <c r="C24" t="n">
         <v>23</v>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
       <c r="D24" t="n">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="E24" t="n">
+        <v>50</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1051</v>
+      </c>
+      <c r="G24" t="n">
+        <v>77</v>
+      </c>
+      <c r="H24" t="n">
+        <v>79</v>
+      </c>
+      <c r="I24" t="n">
         <v>14</v>
-      </c>
-      <c r="F24" t="n">
-        <v>54</v>
-      </c>
-      <c r="G24" t="n">
-        <v>76</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1663</v>
-      </c>
-      <c r="I24" t="n">
-        <v>88</v>
-      </c>
-      <c r="J24" t="n">
-        <v>90</v>
-      </c>
-      <c r="K24" t="n">
-        <v>21</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>24</v>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
+      <c r="C25" t="n">
+        <v>29</v>
       </c>
       <c r="D25" t="n">
+        <v>44</v>
+      </c>
+      <c r="E25" t="n">
         <v>48</v>
       </c>
-      <c r="E25" t="n">
-        <v>29</v>
-      </c>
       <c r="F25" t="n">
-        <v>45</v>
+        <v>1129</v>
       </c>
       <c r="G25" t="n">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="H25" t="n">
-        <v>1629</v>
+        <v>79</v>
       </c>
       <c r="I25" t="n">
-        <v>88</v>
-      </c>
-      <c r="J25" t="n">
-        <v>91</v>
-      </c>
-      <c r="K25" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>25</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Bosnia and Herzegovina</t>
-        </is>
+        <v>62</v>
+      </c>
+      <c r="C26" t="n">
+        <v>26</v>
       </c>
       <c r="D26" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="E26" t="n">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="F26" t="n">
-        <v>43</v>
+        <v>1733</v>
       </c>
       <c r="G26" t="n">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="H26" t="n">
-        <v>1618</v>
+        <v>67</v>
       </c>
       <c r="I26" t="n">
-        <v>81</v>
-      </c>
-      <c r="J26" t="n">
-        <v>76</v>
-      </c>
-      <c r="K26" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
+        <v>31</v>
+      </c>
+      <c r="C27" t="n">
+        <v>32</v>
       </c>
       <c r="D27" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E27" t="n">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="F27" t="n">
-        <v>45</v>
+        <v>914</v>
       </c>
       <c r="G27" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H27" t="n">
-        <v>1569</v>
+        <v>73</v>
       </c>
       <c r="I27" t="n">
-        <v>82</v>
-      </c>
-      <c r="J27" t="n">
-        <v>85</v>
-      </c>
-      <c r="K27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Korea Republic</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Egypt</t>
-        </is>
+        <v>64</v>
+      </c>
+      <c r="C28" t="n">
+        <v>28</v>
       </c>
       <c r="D28" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E28" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="F28" t="n">
-        <v>49</v>
+        <v>1853</v>
       </c>
       <c r="G28" t="n">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="H28" t="n">
-        <v>1543</v>
+        <v>86</v>
       </c>
       <c r="I28" t="n">
-        <v>87</v>
-      </c>
-      <c r="J28" t="n">
-        <v>96</v>
-      </c>
-      <c r="K28" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Croatia</t>
-        </is>
+        <v>42</v>
+      </c>
+      <c r="C29" t="n">
+        <v>31</v>
       </c>
       <c r="D29" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E29" t="n">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="F29" t="n">
-        <v>52</v>
+        <v>1690</v>
       </c>
       <c r="G29" t="n">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="H29" t="n">
-        <v>1515</v>
+        <v>82</v>
       </c>
       <c r="I29" t="n">
-        <v>88</v>
-      </c>
-      <c r="J29" t="n">
-        <v>76</v>
-      </c>
-      <c r="K29" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>29</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Congo DR</t>
-        </is>
+        <v>77</v>
+      </c>
+      <c r="C30" t="n">
+        <v>27</v>
       </c>
       <c r="D30" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="E30" t="n">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="F30" t="n">
-        <v>36</v>
+        <v>2627</v>
       </c>
       <c r="G30" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="H30" t="n">
-        <v>1470</v>
+        <v>81</v>
       </c>
       <c r="I30" t="n">
-        <v>81</v>
-      </c>
-      <c r="J30" t="n">
-        <v>78</v>
-      </c>
-      <c r="K30" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>30</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Austria</t>
-        </is>
+        <v>79</v>
+      </c>
+      <c r="C31" t="n">
+        <v>27</v>
       </c>
       <c r="D31" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="E31" t="n">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="F31" t="n">
-        <v>62</v>
+        <v>2039</v>
       </c>
       <c r="G31" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="H31" t="n">
-        <v>1467</v>
+        <v>82</v>
       </c>
       <c r="I31" t="n">
-        <v>87</v>
-      </c>
-      <c r="J31" t="n">
-        <v>100</v>
-      </c>
-      <c r="K31" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>31</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
+        <v>37</v>
+      </c>
+      <c r="C32" t="n">
+        <v>19</v>
       </c>
       <c r="D32" t="n">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c r="E32" t="n">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="F32" t="n">
-        <v>64</v>
+        <v>1335</v>
       </c>
       <c r="G32" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="H32" t="n">
-        <v>1445</v>
+        <v>75</v>
       </c>
       <c r="I32" t="n">
-        <v>87</v>
-      </c>
-      <c r="J32" t="n">
-        <v>95</v>
-      </c>
-      <c r="K32" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Scotland</t>
-        </is>
+        <v>52</v>
+      </c>
+      <c r="C33" t="n">
+        <v>37</v>
       </c>
       <c r="D33" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="E33" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="F33" t="n">
-        <v>40</v>
+        <v>1849</v>
       </c>
       <c r="G33" t="n">
-        <v>45</v>
+        <v>86</v>
       </c>
       <c r="H33" t="n">
-        <v>1377</v>
+        <v>71</v>
       </c>
       <c r="I33" t="n">
-        <v>87</v>
-      </c>
-      <c r="J33" t="n">
-        <v>71</v>
-      </c>
-      <c r="K33" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>33</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>New Zealand</t>
-        </is>
+        <v>58</v>
+      </c>
+      <c r="C34" t="n">
+        <v>21</v>
       </c>
       <c r="D34" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E34" t="n">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="F34" t="n">
-        <v>22</v>
+        <v>1259</v>
       </c>
       <c r="G34" t="n">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="H34" t="n">
-        <v>1335</v>
+        <v>70</v>
       </c>
       <c r="I34" t="n">
-        <v>83</v>
-      </c>
-      <c r="J34" t="n">
-        <v>75</v>
-      </c>
-      <c r="K34" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>34</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Panama</t>
-        </is>
+        <v>41</v>
+      </c>
+      <c r="C35" t="n">
+        <v>20</v>
       </c>
       <c r="D35" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="E35" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="F35" t="n">
-        <v>43</v>
+        <v>1169</v>
       </c>
       <c r="G35" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="H35" t="n">
-        <v>1259</v>
+        <v>80</v>
       </c>
       <c r="I35" t="n">
-        <v>83</v>
-      </c>
-      <c r="J35" t="n">
-        <v>70</v>
-      </c>
-      <c r="K35" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>35</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Saudi Arabia</t>
-        </is>
+        <v>61</v>
+      </c>
+      <c r="C36" t="n">
+        <v>25</v>
       </c>
       <c r="D36" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="E36" t="n">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="F36" t="n">
-        <v>40</v>
+        <v>1899</v>
       </c>
       <c r="G36" t="n">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="H36" t="n">
-        <v>1175</v>
+        <v>84</v>
       </c>
       <c r="I36" t="n">
-        <v>78</v>
-      </c>
-      <c r="J36" t="n">
-        <v>67</v>
-      </c>
-      <c r="K36" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B37" t="n">
+        <v>28</v>
+      </c>
+      <c r="C37" t="n">
         <v>36</v>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
       <c r="D37" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="E37" t="n">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="F37" t="n">
-        <v>27</v>
+        <v>912</v>
       </c>
       <c r="G37" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="H37" t="n">
-        <v>1169</v>
+        <v>91</v>
       </c>
       <c r="I37" t="n">
-        <v>72</v>
-      </c>
-      <c r="J37" t="n">
-        <v>80</v>
-      </c>
-      <c r="K37" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>37</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Iraq</t>
-        </is>
+        <v>22</v>
+      </c>
+      <c r="C38" t="n">
+        <v>23</v>
       </c>
       <c r="D38" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E38" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="F38" t="n">
-        <v>44</v>
+        <v>1175</v>
       </c>
       <c r="G38" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="H38" t="n">
-        <v>1129</v>
+        <v>67</v>
       </c>
       <c r="I38" t="n">
-        <v>81</v>
-      </c>
-      <c r="J38" t="n">
-        <v>79</v>
-      </c>
-      <c r="K38" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>38</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Australia</t>
-        </is>
+        <v>53</v>
+      </c>
+      <c r="C39" t="n">
+        <v>34</v>
       </c>
       <c r="D39" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E39" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F39" t="n">
-        <v>50</v>
+        <v>1377</v>
       </c>
       <c r="G39" t="n">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="H39" t="n">
-        <v>1127</v>
+        <v>71</v>
       </c>
       <c r="I39" t="n">
-        <v>81</v>
-      </c>
-      <c r="J39" t="n">
-        <v>56</v>
-      </c>
-      <c r="K39" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>39</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Czechia</t>
-        </is>
+        <v>90</v>
+      </c>
+      <c r="C40" t="n">
+        <v>28</v>
       </c>
       <c r="D40" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E40" t="n">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="F40" t="n">
-        <v>38</v>
+        <v>2248</v>
       </c>
       <c r="G40" t="n">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="H40" t="n">
-        <v>1102</v>
+        <v>90</v>
       </c>
       <c r="I40" t="n">
-        <v>79</v>
-      </c>
-      <c r="J40" t="n">
-        <v>75</v>
-      </c>
-      <c r="K40" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>40</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Haiti</t>
-        </is>
+        <v>36</v>
+      </c>
+      <c r="C41" t="n">
+        <v>17</v>
       </c>
       <c r="D41" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E41" t="n">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="F41" t="n">
-        <v>40</v>
+        <v>1855</v>
       </c>
       <c r="G41" t="n">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="H41" t="n">
-        <v>1098</v>
+        <v>85</v>
       </c>
       <c r="I41" t="n">
-        <v>85</v>
-      </c>
-      <c r="J41" t="n">
-        <v>100</v>
-      </c>
-      <c r="K41" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>41</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Cabo Verde</t>
-        </is>
+        <v>82</v>
+      </c>
+      <c r="C42" t="n">
+        <v>22</v>
       </c>
       <c r="D42" t="n">
-        <v>32</v>
+        <v>72</v>
       </c>
       <c r="E42" t="n">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="F42" t="n">
-        <v>34</v>
+        <v>2191</v>
       </c>
       <c r="G42" t="n">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="H42" t="n">
-        <v>1064</v>
+        <v>95</v>
       </c>
       <c r="I42" t="n">
-        <v>80</v>
-      </c>
-      <c r="J42" t="n">
-        <v>65</v>
-      </c>
-      <c r="K42" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>42</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Uzbekistan</t>
-        </is>
+        <v>62</v>
+      </c>
+      <c r="C43" t="n">
+        <v>19</v>
       </c>
       <c r="D43" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="E43" t="n">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="F43" t="n">
-        <v>27</v>
+        <v>1569</v>
       </c>
       <c r="G43" t="n">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="H43" t="n">
-        <v>1059</v>
+        <v>85</v>
       </c>
       <c r="I43" t="n">
-        <v>78</v>
-      </c>
-      <c r="J43" t="n">
-        <v>76</v>
-      </c>
-      <c r="K43" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>43</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>IR Iran</t>
-        </is>
+        <v>66</v>
+      </c>
+      <c r="C44" t="n">
+        <v>14</v>
       </c>
       <c r="D44" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="E44" t="n">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="F44" t="n">
-        <v>46</v>
+        <v>1663</v>
       </c>
       <c r="G44" t="n">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="H44" t="n">
-        <v>1051</v>
+        <v>90</v>
       </c>
       <c r="I44" t="n">
-        <v>77</v>
-      </c>
-      <c r="J44" t="n">
-        <v>79</v>
-      </c>
-      <c r="K44" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>44</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Tunisia</t>
-        </is>
+        <v>35</v>
+      </c>
+      <c r="C45" t="n">
+        <v>23</v>
       </c>
       <c r="D45" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E45" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="F45" t="n">
-        <v>38</v>
+        <v>1011</v>
       </c>
       <c r="G45" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="H45" t="n">
-        <v>1011</v>
+        <v>71</v>
       </c>
       <c r="I45" t="n">
-        <v>80</v>
-      </c>
-      <c r="J45" t="n">
-        <v>71</v>
-      </c>
-      <c r="K45" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>45</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ghana</t>
-        </is>
+        <v>84</v>
+      </c>
+      <c r="C46" t="n">
+        <v>14</v>
       </c>
       <c r="D46" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="E46" t="n">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="F46" t="n">
-        <v>51</v>
+        <v>1844</v>
       </c>
       <c r="G46" t="n">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="H46" t="n">
-        <v>1007</v>
+        <v>73</v>
       </c>
       <c r="I46" t="n">
-        <v>84</v>
-      </c>
-      <c r="J46" t="n">
-        <v>88</v>
-      </c>
-      <c r="K46" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>46</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Curaçao</t>
-        </is>
+        <v>77</v>
+      </c>
+      <c r="C47" t="n">
+        <v>27</v>
       </c>
       <c r="D47" t="n">
+        <v>59</v>
+      </c>
+      <c r="E47" t="n">
+        <v>119</v>
+      </c>
+      <c r="F47" t="n">
+        <v>2053</v>
+      </c>
+      <c r="G47" t="n">
+        <v>86</v>
+      </c>
+      <c r="H47" t="n">
+        <v>81</v>
+      </c>
+      <c r="I47" t="n">
         <v>21</v>
-      </c>
-      <c r="E47" t="n">
-        <v>29</v>
-      </c>
-      <c r="F47" t="n">
-        <v>40</v>
-      </c>
-      <c r="G47" t="n">
-        <v>40</v>
-      </c>
-      <c r="H47" t="n">
-        <v>968</v>
-      </c>
-      <c r="I47" t="n">
-        <v>80</v>
-      </c>
-      <c r="J47" t="n">
-        <v>100</v>
-      </c>
-      <c r="K47" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>47</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
+        <v>87</v>
+      </c>
+      <c r="C48" t="n">
+        <v>21</v>
       </c>
       <c r="D48" t="n">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="E48" t="n">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="F48" t="n">
-        <v>52</v>
+        <v>1445</v>
       </c>
       <c r="G48" t="n">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="H48" t="n">
-        <v>914</v>
+        <v>95</v>
       </c>
       <c r="I48" t="n">
-        <v>76</v>
-      </c>
-      <c r="J48" t="n">
-        <v>73</v>
-      </c>
-      <c r="K48" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Distribution</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>48</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Qatar</t>
-        </is>
+        <v>34</v>
+      </c>
+      <c r="C49" t="n">
+        <v>18</v>
       </c>
       <c r="D49" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E49" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="F49" t="n">
-        <v>27</v>
+        <v>1059</v>
       </c>
       <c r="G49" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="H49" t="n">
-        <v>912</v>
+        <v>76</v>
       </c>
       <c r="I49" t="n">
-        <v>78</v>
-      </c>
-      <c r="J49" t="n">
-        <v>91</v>
-      </c>
-      <c r="K49" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -2382,7 +1986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2441,279 +2045,248 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Rank</t>
+          <t>Crosses</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>48</v>
       </c>
       <c r="C2" t="n">
-        <v>24.5</v>
+        <v>57.97916666666666</v>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>26.09433751515087</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F2" t="n">
-        <v>12.75</v>
+        <v>36.75</v>
       </c>
       <c r="G2" t="n">
-        <v>24.5</v>
+        <v>53</v>
       </c>
       <c r="H2" t="n">
-        <v>36.25</v>
+        <v>77</v>
       </c>
       <c r="I2" t="n">
-        <v>48</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Crosses</t>
+          <t>Crossing Accuracy (%)</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>48</v>
       </c>
       <c r="C3" t="n">
-        <v>57.97916666666666</v>
+        <v>24.5625</v>
       </c>
       <c r="D3" t="n">
-        <v>26.09433751515087</v>
+        <v>5.565494950366337</v>
       </c>
       <c r="E3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F3" t="n">
         <v>21</v>
       </c>
-      <c r="F3" t="n">
-        <v>36.75</v>
-      </c>
       <c r="G3" t="n">
-        <v>53</v>
+        <v>24.5</v>
       </c>
       <c r="H3" t="n">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="I3" t="n">
-        <v>131</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Crossing Accuracy (%)</t>
+          <t>Defensive Linebreaks Acc (%)</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>48</v>
       </c>
       <c r="C4" t="n">
-        <v>24.5625</v>
+        <v>48.60416666666666</v>
       </c>
       <c r="D4" t="n">
-        <v>5.565494950366337</v>
+        <v>11.47937944674143</v>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F4" t="n">
-        <v>21</v>
+        <v>40.75</v>
       </c>
       <c r="G4" t="n">
-        <v>24.5</v>
+        <v>49.5</v>
       </c>
       <c r="H4" t="n">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="I4" t="n">
-        <v>37</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Defensive Linebreaks Acc (%)</t>
+          <t>Defensive Linebreaks Attempted</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>48</v>
       </c>
       <c r="C5" t="n">
-        <v>48.60416666666666</v>
+        <v>67.52083333333333</v>
       </c>
       <c r="D5" t="n">
-        <v>11.47937944674143</v>
+        <v>20.05417087549485</v>
       </c>
       <c r="E5" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="F5" t="n">
-        <v>40.75</v>
+        <v>51.75</v>
       </c>
       <c r="G5" t="n">
-        <v>49.5</v>
+        <v>67.5</v>
       </c>
       <c r="H5" t="n">
-        <v>57</v>
+        <v>78.25</v>
       </c>
       <c r="I5" t="n">
-        <v>72</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Defensive Linebreaks Attempted</t>
+          <t>Passes</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>48</v>
       </c>
       <c r="C6" t="n">
-        <v>67.52083333333333</v>
+        <v>1629.916666666667</v>
       </c>
       <c r="D6" t="n">
-        <v>20.05417087549485</v>
+        <v>484.5246775145384</v>
       </c>
       <c r="E6" t="n">
-        <v>40</v>
+        <v>912</v>
       </c>
       <c r="F6" t="n">
-        <v>51.75</v>
+        <v>1159</v>
       </c>
       <c r="G6" t="n">
-        <v>67.5</v>
+        <v>1623.5</v>
       </c>
       <c r="H6" t="n">
-        <v>78.25</v>
+        <v>1973.75</v>
       </c>
       <c r="I6" t="n">
-        <v>119</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Passes</t>
+          <t>Passing Accuracy (%)</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>48</v>
       </c>
       <c r="C7" t="n">
-        <v>1629.916666666667</v>
+        <v>84.83333333333333</v>
       </c>
       <c r="D7" t="n">
-        <v>484.5246775145384</v>
+        <v>4.719057484932695</v>
       </c>
       <c r="E7" t="n">
-        <v>912</v>
+        <v>72</v>
       </c>
       <c r="F7" t="n">
-        <v>1159</v>
+        <v>81</v>
       </c>
       <c r="G7" t="n">
-        <v>1623.5</v>
+        <v>86</v>
       </c>
       <c r="H7" t="n">
-        <v>1973.75</v>
+        <v>88</v>
       </c>
       <c r="I7" t="n">
-        <v>2721</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Passing Accuracy (%)</t>
+          <t>Switches of Play Acc (%)</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>84.83333333333333</v>
+        <v>81.91666666666667</v>
       </c>
       <c r="D8" t="n">
-        <v>4.719057484932694</v>
+        <v>10.4511698079502</v>
       </c>
       <c r="E8" t="n">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="F8" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="G8" t="n">
         <v>81</v>
       </c>
-      <c r="G8" t="n">
-        <v>86</v>
-      </c>
       <c r="H8" t="n">
-        <v>88</v>
+        <v>90.25</v>
       </c>
       <c r="I8" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Switches of Play Acc (%)</t>
+          <t>Switches of Play Attempted</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>81.91666666666667</v>
+        <v>17.35416666666667</v>
       </c>
       <c r="D9" t="n">
-        <v>10.4511698079502</v>
+        <v>6.054678456010175</v>
       </c>
       <c r="E9" t="n">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="F9" t="n">
-        <v>74.5</v>
+        <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="H9" t="n">
-        <v>90.25</v>
+        <v>21</v>
       </c>
       <c r="I9" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Switches of Play Attempted</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>48</v>
-      </c>
-      <c r="C10" t="n">
-        <v>17.35416666666667</v>
-      </c>
-      <c r="D10" t="n">
-        <v>6.054678456010175</v>
-      </c>
-      <c r="E10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F10" t="n">
-        <v>13</v>
-      </c>
-      <c r="G10" t="n">
-        <v>17</v>
-      </c>
-      <c r="H10" t="n">
-        <v>21</v>
-      </c>
-      <c r="I10" t="n">
         <v>32</v>
       </c>
     </row>

--- a/outputs/fifa_team_statistics/excel_por_categoria/Distribution.xlsx
+++ b/outputs/fifa_team_statistics/excel_por_categoria/Distribution.xlsx
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" t="n">
         <v>62</v>
@@ -599,10 +599,10 @@
         <v>60</v>
       </c>
       <c r="F5" t="n">
-        <v>1467</v>
+        <v>1824</v>
       </c>
       <c r="G5" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H5" t="n">
         <v>100</v>
@@ -1734,10 +1734,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="C42" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D42" t="n">
         <v>72</v>
@@ -1746,7 +1746,7 @@
         <v>78</v>
       </c>
       <c r="F42" t="n">
-        <v>2191</v>
+        <v>2831</v>
       </c>
       <c r="G42" t="n">
         <v>92</v>
@@ -2052,10 +2052,10 @@
         <v>48</v>
       </c>
       <c r="C2" t="n">
-        <v>57.97916666666666</v>
+        <v>58.6875</v>
       </c>
       <c r="D2" t="n">
-        <v>26.09433751515087</v>
+        <v>26.70337953749308</v>
       </c>
       <c r="E2" t="n">
         <v>21</v>
@@ -2064,7 +2064,7 @@
         <v>36.75</v>
       </c>
       <c r="G2" t="n">
-        <v>53</v>
+        <v>55.5</v>
       </c>
       <c r="H2" t="n">
         <v>77</v>
@@ -2083,10 +2083,10 @@
         <v>48</v>
       </c>
       <c r="C3" t="n">
-        <v>24.5625</v>
+        <v>24.60416666666667</v>
       </c>
       <c r="D3" t="n">
-        <v>5.565494950366337</v>
+        <v>5.545707879660163</v>
       </c>
       <c r="E3" t="n">
         <v>14</v>
@@ -2176,10 +2176,10 @@
         <v>48</v>
       </c>
       <c r="C6" t="n">
-        <v>1629.916666666667</v>
+        <v>1650.6875</v>
       </c>
       <c r="D6" t="n">
-        <v>484.5246775145384</v>
+        <v>508.4837768599774</v>
       </c>
       <c r="E6" t="n">
         <v>912</v>
@@ -2188,13 +2188,13 @@
         <v>1159</v>
       </c>
       <c r="G6" t="n">
-        <v>1623.5</v>
+        <v>1646</v>
       </c>
       <c r="H6" t="n">
         <v>1973.75</v>
       </c>
       <c r="I6" t="n">
-        <v>2721</v>
+        <v>2831</v>
       </c>
     </row>
     <row r="7">
@@ -2207,10 +2207,10 @@
         <v>48</v>
       </c>
       <c r="C7" t="n">
-        <v>84.83333333333333</v>
+        <v>84.8125</v>
       </c>
       <c r="D7" t="n">
-        <v>4.719057484932695</v>
+        <v>4.711490029478184</v>
       </c>
       <c r="E7" t="n">
         <v>72</v>
